--- a/data/trans_camb/P42C_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P42C_R-Estudios-trans_camb.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -506,8 +506,6 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,22 +517,16 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -555,16 +547,6 @@
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2012</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2012</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2023/2012</t>
         </is>
@@ -577,8 +559,6 @@
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -593,12 +573,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-9,12</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-6,47</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -607,16 +587,6 @@
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-6,47</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-9,12</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-6,47</t>
         </is>
@@ -631,32 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,91; -6,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,24; -3,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,78; -6,5</t>
+          <t>-11,91; -6,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,27; -3,04</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-11,78; -6,5</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-9,27; -3,04</t>
+          <t>-9,24; -3,38</t>
         </is>
       </c>
     </row>
@@ -669,12 +629,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-71,67%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-50,84%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -683,16 +643,6 @@
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-50,84%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-71,67%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-50,84%</t>
         </is>
@@ -707,32 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,38; -56,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-65,66; -28,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-82,61; -54,72</t>
+          <t>-82,38; -56,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-65,81; -25,61</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-82,61; -54,72</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-65,81; -25,61</t>
+          <t>-65,66; -28,55</t>
         </is>
       </c>
     </row>
@@ -749,12 +689,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-11,24</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4,76</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -763,16 +703,6 @@
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-4,76</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-11,24</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>-4,76</t>
         </is>
@@ -787,32 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,18; -8,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,44; -1,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,3; -8,09</t>
+          <t>-14,18; -8,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,09; -1,02</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-14,3; -8,09</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-9,09; -1,02</t>
+          <t>-9,44; -1,11</t>
         </is>
       </c>
     </row>
@@ -825,12 +745,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-44,15%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-18,7%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -839,16 +759,6 @@
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-18,7%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-44,15%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>-18,7%</t>
         </is>
@@ -863,32 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-52,25; -34,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-35,89; -4,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,96; -34,04</t>
+          <t>-52,25; -34,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,55; -5,0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-51,96; -34,04</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-34,55; -5,0</t>
+          <t>-35,89; -4,97</t>
         </is>
       </c>
     </row>
@@ -905,12 +805,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-9,0</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,94</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -919,16 +819,6 @@
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,94</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-9,0</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,94</t>
         </is>
@@ -943,32 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-15,57; -2,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,21; 9,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,33; -1,44</t>
+          <t>-15,57; -2,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 8,91</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-15,33; -1,44</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-5,14; 8,91</t>
+          <t>-4,21; 9,98</t>
         </is>
       </c>
     </row>
@@ -981,12 +861,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-19,7%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -995,16 +875,6 @@
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-19,7%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6,44%</t>
         </is>
@@ -1019,32 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-31,8; -6,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,27; 24,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,48; -3,59</t>
+          <t>-31,8; -6,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 21,17</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-31,48; -3,59</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-10,66; 21,17</t>
+          <t>-8,27; 24,21</t>
         </is>
       </c>
     </row>
@@ -1061,12 +921,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-8,45</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1075,16 +935,6 @@
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,76</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-8,45</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>-0,76</t>
         </is>
@@ -1099,32 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,63; -6,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,66; 2,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,51; -6,34</t>
+          <t>-10,63; -6,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,93</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-10,51; -6,34</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-4,01; 1,93</t>
+          <t>-3,66; 2,19</t>
         </is>
       </c>
     </row>
@@ -1137,12 +977,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-35,31%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-3,16%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1151,16 +991,6 @@
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-3,16%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-35,31%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>-3,16%</t>
         </is>
@@ -1175,32 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-42,16; -27,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,58; 9,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,92; -27,58</t>
+          <t>-42,16; -27,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 8,43</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-41,92; -27,58</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-15,86; 8,43</t>
+          <t>-14,58; 9,4</t>
         </is>
       </c>
     </row>
@@ -1212,11 +1032,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="C1:D1"/>
-    <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="A1:B2"/>

--- a/data/trans_camb/P42C_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P42C_R-Estudios-trans_camb.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-6,47</t>
+          <t>-6,57</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,47</t>
+          <t>-6,57</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,91; -6,51</t>
+          <t>-11,68; -6,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -3,38</t>
+          <t>-9,52; -3,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,91; -6,51</t>
+          <t>-11,68; -6,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -3,38</t>
+          <t>-9,52; -3,65</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-50,84%</t>
+          <t>-51,64%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-50,84%</t>
+          <t>-51,64%</t>
         </is>
       </c>
     </row>
@@ -657,22 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-82,38; -56,29</t>
+          <t>-82,08; -55,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-65,66; -28,55</t>
+          <t>-65,23; -31,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-82,38; -56,29</t>
+          <t>-82,08; -55,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-65,66; -28,55</t>
+          <t>-65,23; -31,94</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-4,76</t>
+          <t>-2,92</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,76</t>
+          <t>-2,92</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,18; -8,18</t>
+          <t>-14,37; -8,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,44; -1,11</t>
+          <t>-6,28; 0,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,18; -8,18</t>
+          <t>-14,37; -8,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,44; -1,11</t>
+          <t>-6,28; 0,49</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-18,7%</t>
+          <t>-11,46%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-18,7%</t>
+          <t>-11,46%</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,25; -34,64</t>
+          <t>-52,56; -33,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,89; -4,97</t>
+          <t>-22,86; 2,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,25; -34,64</t>
+          <t>-52,56; -33,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,89; -4,97</t>
+          <t>-22,86; 2,36</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>2,15</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,57; -2,78</t>
+          <t>-15,89; -2,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 9,98</t>
+          <t>-4,33; 8,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,57; -2,78</t>
+          <t>-15,89; -2,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 9,98</t>
+          <t>-4,33; 8,91</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -889,22 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,8; -6,63</t>
+          <t>-32,77; -5,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 24,21</t>
+          <t>-8,78; 21,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,8; -6,63</t>
+          <t>-32,77; -5,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 24,21</t>
+          <t>-8,78; 21,43</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>0,36</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,63; -6,27</t>
+          <t>-10,67; -6,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 2,19</t>
+          <t>-1,96; 2,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,63; -6,27</t>
+          <t>-10,67; -6,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 2,19</t>
+          <t>-1,96; 2,56</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-3,16%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-3,16%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,16; -27,62</t>
+          <t>-42,71; -27,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 9,4</t>
+          <t>-7,55; 11,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,16; -27,62</t>
+          <t>-42,71; -27,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 9,4</t>
+          <t>-7,55; 11,22</t>
         </is>
       </c>
     </row>
